--- a/ocr/test.xlsx
+++ b/ocr/test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="103">
   <si>
     <t>vendor_name</t>
   </si>
@@ -100,24 +100,36 @@
     <t>campaigns_duration</t>
   </si>
   <si>
-    <t>VOUCHER SERVICES SA</t>
-  </si>
-  <si>
     <t>Meta Platforms Ireland Limited</t>
   </si>
   <si>
+    <t>Google Ireland Limited</t>
+  </si>
+  <si>
     <t>00709</t>
   </si>
   <si>
-    <t>EL094438998</t>
-  </si>
-  <si>
     <t>IE9692928F</t>
   </si>
   <si>
+    <t>IE6388047V</t>
+  </si>
+  <si>
+    <t>FBADS-266-104141116</t>
+  </si>
+  <si>
+    <t>5174183378</t>
+  </si>
+  <si>
     <t>FBADS-266-104173647</t>
   </si>
   <si>
+    <t>FBADS-266-104152018</t>
+  </si>
+  <si>
+    <t>FBADS-673-104093782</t>
+  </si>
+  <si>
     <t>FBADS-673-104054613</t>
   </si>
   <si>
@@ -142,15 +154,21 @@
     <t>FBADS-266-104162933</t>
   </si>
   <si>
+    <t>15/01/2025</t>
+  </si>
+  <si>
+    <t>31/01/2025</t>
+  </si>
+  <si>
     <t>26/01/2025</t>
   </si>
   <si>
+    <t>18/01/2025</t>
+  </si>
+  <si>
     <t>16/01/2025</t>
   </si>
   <si>
-    <t>31/01/2025</t>
-  </si>
-  <si>
     <t>07/01/2025</t>
   </si>
   <si>
@@ -175,16 +193,22 @@
     <t>01/03/2025</t>
   </si>
   <si>
+    <t>Invoice for Meta ads campaign</t>
+  </si>
+  <si>
+    <t>Invoice for Google Ads services</t>
+  </si>
+  <si>
     <t>Invoice for Meta ads services</t>
   </si>
   <si>
-    <t>Invoice for Meta ads</t>
-  </si>
-  <si>
-    <t>Meta ads spend for campaigns</t>
-  </si>
-  <si>
-    <t>Invoice for Meta ads campaign</t>
+    <t>Meta ads campaign expenses</t>
+  </si>
+  <si>
+    <t>Meta ads for New Year Giveaway and Όραμα καριέρας</t>
+  </si>
+  <si>
+    <t>Ads spend for New Year Giveaway (2025)</t>
   </si>
   <si>
     <t>Electronic Transfer</t>
@@ -196,6 +220,9 @@
     <t>Paid</t>
   </si>
   <si>
+    <t>60 Days after Invoice Date</t>
+  </si>
+  <si>
     <t>000</t>
   </si>
   <si>
@@ -208,6 +235,9 @@
     <t>['Spendeo', 'Ticket Restaurant']</t>
   </si>
   <si>
+    <t>['Ticket Restaurant', 'Ticket Compliments', 'Ticket Restaurant Paper', 'MyBenefits', 'Spendeo', 'Spendeo Plus']</t>
+  </si>
+  <si>
     <t>['Ticket Restaurant']</t>
   </si>
   <si>
@@ -217,7 +247,19 @@
     <t>0000</t>
   </si>
   <si>
-    <t>{'Ticket Restaurant': 749.47, 'Spendeo': 50.53}</t>
+    <t>{'Ticket Restaurant': 748.03, 'Spendeo': 51.97}</t>
+  </si>
+  <si>
+    <t>{'Ticket Restaurant': 6705.29, 'Ticket Compliments': 5249.86}</t>
+  </si>
+  <si>
+    <t>{'Ticket Restaurant': 800.0, 'Spendeo': 50.53}</t>
+  </si>
+  <si>
+    <t>{'Spendeo': 57.19, 'Ticket Restaurant': 742.81}</t>
+  </si>
+  <si>
+    <t>{'Βελτίωση σχέσεων με συναδέλφους': 99.97, 'Post: Sovolos Bakery': 50.0, 'Post: Employee Experience Pulse Zoe Fragou (Video)': 250.0, 'Όραμα καριέρας': 75.08, 'New Year Giveaway (2025)': 49.57}</t>
   </si>
   <si>
     <t>{'New Year Giveaway (2025)': 725.17, 'Όραμα καριέρας': 74.83}</t>
@@ -244,16 +286,28 @@
     <t>{'Spendeo': 58.46, 'Ticket Restaurant': 741.54}</t>
   </si>
   <si>
+    <t>['From 10/01/2025 to 15/01/2025']</t>
+  </si>
+  <si>
+    <t>['1/1/2025 - 31/1/2025']</t>
+  </si>
+  <si>
     <t>['From 21/01/2025 to 26/01/2025']</t>
   </si>
   <si>
-    <t>['From 11/01/2025 to 16/01/2025', 'From 11/01/2025 to 16/01/2025']</t>
+    <t>['From 14/01/2025 to 18/01/2025']</t>
+  </si>
+  <si>
+    <t>['From 16/01/2025 to 30/01/2025']</t>
+  </si>
+  <si>
+    <t>['From 11/01/2025 to 16/01/2025']</t>
   </si>
   <si>
     <t>['From 28/01/2025 to 30/01/2025']</t>
   </si>
   <si>
-    <t>['From Jan 3, 2025, 12:00 AM to Jan 7, 2025, 9:02 PM']</t>
+    <t>['From 03/01/2025 to 07/01/2025']</t>
   </si>
   <si>
     <t>['From 25/01/2025 to 29/01/2025']</t>
@@ -262,10 +316,10 @@
     <t>['From 06/01/2025 to 11/01/2025']</t>
   </si>
   <si>
-    <t>['From 30/12/2024, 12:00 AM to 04/01/2025, 7:54 AM']</t>
-  </si>
-  <si>
-    <t>['From Jan 10, 2025, 12:00 AM to Jan 11, 2025, 11:59 PM']</t>
+    <t>['From 30/12/2024 to 04/01/2025']</t>
+  </si>
+  <si>
+    <t>['From 10/01/2025 to 11/01/2025']</t>
   </si>
   <si>
     <t>['From 18/01/2025 to 22/01/2025']</t>
@@ -626,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AB14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:28">
@@ -729,132 +783,132 @@
         <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J2">
         <v>800</v>
       </c>
       <c r="K2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="M2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="N2" t="s">
+        <v>67</v>
+      </c>
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2">
+        <v>800</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="T2" t="s">
+        <v>69</v>
+      </c>
+      <c r="U2" t="s">
+        <v>70</v>
+      </c>
+      <c r="W2" t="s">
+        <v>75</v>
+      </c>
+      <c r="X2" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y2" t="s">
         <v>59</v>
       </c>
-      <c r="O2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2">
-        <v>645.16</v>
-      </c>
-      <c r="Q2">
-        <v>154.84</v>
-      </c>
-      <c r="T2" t="s">
-        <v>60</v>
-      </c>
-      <c r="U2" t="s">
-        <v>61</v>
-      </c>
-      <c r="W2" t="s">
-        <v>65</v>
-      </c>
-      <c r="X2" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>53</v>
-      </c>
       <c r="AA2" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="AB2" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:28">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
         <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J3">
-        <v>800</v>
+        <v>23732.65</v>
       </c>
       <c r="K3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="M3" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="N3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="O3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P3">
-        <v>645.16</v>
+        <v>23732.65</v>
       </c>
       <c r="Q3">
-        <v>154.84</v>
+        <v>0</v>
       </c>
       <c r="T3" t="s">
+        <v>69</v>
+      </c>
+      <c r="U3" t="s">
+        <v>71</v>
+      </c>
+      <c r="W3" t="s">
+        <v>75</v>
+      </c>
+      <c r="X3" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y3" t="s">
         <v>60</v>
       </c>
-      <c r="U3" t="s">
-        <v>62</v>
-      </c>
-      <c r="W3" t="s">
-        <v>65</v>
-      </c>
-      <c r="X3" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>54</v>
-      </c>
       <c r="AA3" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="AB3" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:28">
@@ -871,105 +925,105 @@
         <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J4">
-        <v>249.86</v>
+        <v>800</v>
       </c>
       <c r="K4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="M4" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="N4" t="s">
+        <v>67</v>
+      </c>
+      <c r="O4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4">
+        <v>800</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="T4" t="s">
+        <v>69</v>
+      </c>
+      <c r="U4" t="s">
+        <v>70</v>
+      </c>
+      <c r="W4" t="s">
+        <v>75</v>
+      </c>
+      <c r="X4" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y4" t="s">
         <v>59</v>
       </c>
-      <c r="O4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P4">
-        <v>201.5</v>
-      </c>
-      <c r="Q4">
-        <v>48.36</v>
-      </c>
-      <c r="T4" t="s">
-        <v>60</v>
-      </c>
-      <c r="U4" t="s">
-        <v>61</v>
-      </c>
-      <c r="W4" t="s">
-        <v>65</v>
-      </c>
-      <c r="X4" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>55</v>
-      </c>
       <c r="AA4" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="AB4" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:28">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
         <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J5">
         <v>800</v>
       </c>
       <c r="K5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L5" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="M5" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="N5" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="O5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P5">
         <v>800</v>
@@ -978,140 +1032,140 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="U5" t="s">
+        <v>72</v>
+      </c>
+      <c r="W5" t="s">
+        <v>75</v>
+      </c>
+      <c r="X5" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y5" t="s">
         <v>61</v>
       </c>
-      <c r="W5" t="s">
-        <v>65</v>
-      </c>
-      <c r="X5" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>53</v>
-      </c>
       <c r="AA5" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB5" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:28">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
         <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G6" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J6">
-        <v>800</v>
+        <v>524.62</v>
       </c>
       <c r="K6" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L6" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="M6" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="N6" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="O6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P6">
-        <v>800</v>
+        <v>524.62</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="U6" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="W6" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="X6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="Y6" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="AA6" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AB6" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:28">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
         <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J7">
         <v>800</v>
       </c>
       <c r="K7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L7" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="M7" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="N7" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="O7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P7">
         <v>800</v>
@@ -1120,211 +1174,211 @@
         <v>0</v>
       </c>
       <c r="T7" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="U7" t="s">
+        <v>71</v>
+      </c>
+      <c r="W7" t="s">
+        <v>75</v>
+      </c>
+      <c r="X7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y7" t="s">
         <v>63</v>
       </c>
-      <c r="W7" t="s">
-        <v>65</v>
-      </c>
-      <c r="X7" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>53</v>
-      </c>
       <c r="AA7" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AB7" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:28">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
         <v>39</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G8" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J8">
-        <v>800</v>
+        <v>249.86</v>
       </c>
       <c r="K8" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M8" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="N8" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="O8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P8">
-        <v>800</v>
+        <v>249.86</v>
       </c>
       <c r="Q8">
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="U8" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="W8" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="X8" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="Y8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AA8" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AB8" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:28">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
         <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J9">
-        <v>225.2</v>
+        <v>800</v>
       </c>
       <c r="K9" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="M9" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="N9" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="O9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P9">
-        <v>225.2</v>
+        <v>800</v>
       </c>
       <c r="Q9">
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="U9" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="W9" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="X9" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="Y9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AA9" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AB9" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:28">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
         <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J10">
         <v>800</v>
       </c>
       <c r="K10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L10" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="M10" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="N10" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="O10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P10">
         <v>800</v>
@@ -1333,25 +1387,309 @@
         <v>0</v>
       </c>
       <c r="T10" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="U10" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="W10" t="s">
+        <v>75</v>
+      </c>
+      <c r="X10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>58</v>
+      </c>
+      <c r="J11">
+        <v>800</v>
+      </c>
+      <c r="K11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M11" t="s">
         <v>65</v>
       </c>
-      <c r="X10" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y10" t="s">
+      <c r="N11" t="s">
+        <v>67</v>
+      </c>
+      <c r="O11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P11">
+        <v>800</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="T11" t="s">
+        <v>69</v>
+      </c>
+      <c r="U11" t="s">
+        <v>72</v>
+      </c>
+      <c r="W11" t="s">
+        <v>75</v>
+      </c>
+      <c r="X11" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" t="s">
         <v>54</v>
       </c>
-      <c r="AA10" t="s">
+      <c r="G12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
+        <v>58</v>
+      </c>
+      <c r="J12">
+        <v>800</v>
+      </c>
+      <c r="K12" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" t="s">
+        <v>61</v>
+      </c>
+      <c r="M12" t="s">
+        <v>65</v>
+      </c>
+      <c r="N12" t="s">
+        <v>67</v>
+      </c>
+      <c r="O12" t="s">
+        <v>31</v>
+      </c>
+      <c r="P12">
+        <v>800</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="T12" t="s">
+        <v>69</v>
+      </c>
+      <c r="U12" t="s">
+        <v>72</v>
+      </c>
+      <c r="W12" t="s">
         <v>75</v>
       </c>
-      <c r="AB10" t="s">
-        <v>84</v>
+      <c r="X12" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13">
+        <v>225.2</v>
+      </c>
+      <c r="K13" t="s">
+        <v>57</v>
+      </c>
+      <c r="L13" t="s">
+        <v>64</v>
+      </c>
+      <c r="M13" t="s">
+        <v>65</v>
+      </c>
+      <c r="N13" t="s">
+        <v>67</v>
+      </c>
+      <c r="O13" t="s">
+        <v>31</v>
+      </c>
+      <c r="P13">
+        <v>225.2</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="T13" t="s">
+        <v>69</v>
+      </c>
+      <c r="U13" t="s">
+        <v>74</v>
+      </c>
+      <c r="W13" t="s">
+        <v>75</v>
+      </c>
+      <c r="X13" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14">
+        <v>800</v>
+      </c>
+      <c r="K14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" t="s">
+        <v>61</v>
+      </c>
+      <c r="M14" t="s">
+        <v>65</v>
+      </c>
+      <c r="N14" t="s">
+        <v>67</v>
+      </c>
+      <c r="O14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P14">
+        <v>800</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="T14" t="s">
+        <v>69</v>
+      </c>
+      <c r="U14" t="s">
+        <v>72</v>
+      </c>
+      <c r="W14" t="s">
+        <v>75</v>
+      </c>
+      <c r="X14" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
